--- a/data/trans_dic/P5B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia</t>
+          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -653,12 +654,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -673,7 +674,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -693,7 +694,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,2</t>
+          <t>0,88; 7,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,24</t>
+          <t>0,46; 4,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,47</t>
+          <t>1,03; 9,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,7</t>
+          <t>0,73; 6,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 6,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,02</t>
+          <t>0,86; 4,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,1</t>
+          <t>0,41; 3,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,2</t>
+          <t>0,29; 2,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,98</t>
+          <t>0,98; 5,77</t>
         </is>
       </c>
     </row>
@@ -798,7 +799,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -823,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -838,7 +839,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,76</t>
+          <t>1,35; 5,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,77</t>
+          <t>0,89; 5,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,71</t>
+          <t>0,78; 4,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,28</t>
+          <t>2,33; 6,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,62</t>
+          <t>0,8; 4,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,13</t>
+          <t>0,32; 3,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,43</t>
+          <t>0,88; 5,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,46</t>
+          <t>2,29; 5,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,91</t>
+          <t>1,25; 4,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,01</t>
+          <t>0,81; 2,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,27</t>
+          <t>0,73; 3,37</t>
         </is>
       </c>
     </row>
@@ -938,7 +939,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,82</t>
+          <t>2,15; 9,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,72</t>
+          <t>0,9; 5,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,43</t>
+          <t>1,42; 5,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,74</t>
+          <t>0,71; 3,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1074,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1083,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1123,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,28</t>
+          <t>2,24; 7,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,67</t>
+          <t>1,23; 6,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,7</t>
+          <t>0,0; 36,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,86</t>
+          <t>1,3; 6,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,0</t>
+          <t>0,46; 4,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,42</t>
+          <t>0,0; 3,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,68</t>
+          <t>0,37; 2,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,86</t>
+          <t>2,37; 5,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,5</t>
+          <t>1,06; 4,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,5</t>
+          <t>0,24; 2,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 25,19</t>
+          <t>0,57; 21,96</t>
         </is>
       </c>
     </row>
@@ -1213,49 +1214,49 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>1,78%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
@@ -1263,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,46</t>
+          <t>2,55; 5,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,13</t>
+          <t>1,13; 3,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,77</t>
+          <t>1,07; 2,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 19,72</t>
+          <t>0,5; 16,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,41</t>
+          <t>1,91; 4,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,59</t>
+          <t>0,84; 2,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,09</t>
+          <t>0,58; 2,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,11</t>
+          <t>0,69; 2,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,31</t>
+          <t>2,64; 4,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,54</t>
+          <t>1,14; 2,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,11</t>
+          <t>0,93; 2,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 9,57</t>
+          <t>0,89; 9,47</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia (tasa de respuesta: 99,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1610</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2207</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4138</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2405</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3334</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>692; 5641</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3428</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>467; 4601</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>592; 5379</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>649; 5436</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5467</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3976</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4077</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1433; 8301</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>886; 7151</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>576; 5761</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1170; 6861</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5465</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4218</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3625</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1441</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8141</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4223</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>13606</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8441</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6279</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5867</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2522; 10704</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1417; 8572</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1215; 7492</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4322</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4388; 12739</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1544; 8338</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>669; 6367</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1600; 9990</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>8617; 21266</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4391; 14219</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2940; 10840</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2479; 11482</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4636</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3464</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5809</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4812</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1862; 8476</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3978</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1295; 7310</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4021</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3246</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4422</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4667</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2702; 10791</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4813</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1951; 9159</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4530</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3616</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27634</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4578</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3279</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11642</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5538</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2159</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>30912</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3377; 11876</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1414; 7471</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2671</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 99551</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1919; 9270</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>601; 5374</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4741</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1125; 7820</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>7090; 17813</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2623; 9886</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>614; 6194</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3314; 127422</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>19275</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9636</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31282</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9741</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>35195</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17986</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15655</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>41023</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>12821; 26356</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5359; 15093</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5589; 15446</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3343; 110326</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10112; 22704</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4495; 14371</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3294; 11606</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5221; 17062</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>27284; 46386</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>11532; 26127</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>10137; 22690</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>12694; 134992</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P5B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,18</t>
+          <t>0,88; 8,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,5</t>
+          <t>0,46; 4,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,35</t>
+          <t>1,15; 9,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,14</t>
+          <t>0,74; 6,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,97</t>
+          <t>0,82; 4,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,33</t>
+          <t>0,31; 3,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,87</t>
+          <t>0,29; 2,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,77</t>
+          <t>1,08; 6,03</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,72</t>
+          <t>1,42; 5,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,38</t>
+          <t>1,08; 5,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,83</t>
+          <t>1,0; 4,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,75</t>
+          <t>2,34; 7,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,32</t>
+          <t>0,72; 4,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,03</t>
+          <t>0,31; 2,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,49</t>
+          <t>0,82; 5,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,66</t>
+          <t>2,41; 5,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,03</t>
+          <t>1,3; 4,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,97</t>
+          <t>0,73; 3,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,37</t>
+          <t>0,79; 3,48</t>
         </is>
       </c>
     </row>
@@ -997,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 9,8</t>
+          <t>2,28; 10,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,09</t>
+          <t>0,89; 5,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,37 +1017,37 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,69</t>
+          <t>1,59; 5,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,32</t>
+          <t>0,71; 3,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,86</t>
+          <t>2,38; 8,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,5</t>
+          <t>1,23; 6,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,24</t>
+          <t>0,0; 36,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,26</t>
+          <t>1,3; 6,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,08</t>
+          <t>0,46; 3,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,56</t>
+          <t>0,38; 2,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,95</t>
+          <t>2,29; 5,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,01</t>
+          <t>1,05; 4,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,46</t>
+          <t>0,24; 2,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 21,96</t>
+          <t>0,49; 20,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,24</t>
+          <t>2,7; 5,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,17</t>
+          <t>1,09; 3,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,95</t>
+          <t>1,04; 2,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 16,58</t>
+          <t>0,49; 18,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,3</t>
+          <t>2,0; 4,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,67</t>
+          <t>0,86; 2,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,03</t>
+          <t>0,55; 2,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,24</t>
+          <t>0,74; 2,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,5</t>
+          <t>2,58; 4,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,58</t>
+          <t>1,19; 2,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,08</t>
+          <t>0,91; 2,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,47</t>
+          <t>0,89; 10,9</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>692; 5641</t>
+          <t>688; 6299</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3428</t>
+          <t>0; 3958</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>467; 4601</t>
+          <t>467; 4873</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>592; 5379</t>
+          <t>662; 5338</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>649; 5436</t>
+          <t>653; 5307</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5467</t>
+          <t>0; 5372</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3976</t>
+          <t>0; 3946</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4077</t>
+          <t>0; 3799</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1433; 8301</t>
+          <t>1372; 8311</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>886; 7151</t>
+          <t>674; 6779</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>576; 5761</t>
+          <t>576; 5660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1170; 6861</t>
+          <t>1283; 7169</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2522; 10704</t>
+          <t>2654; 10720</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1417; 8572</t>
+          <t>1721; 8047</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1215; 7492</t>
+          <t>1549; 7352</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4322</t>
+          <t>0; 5479</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4388; 12739</t>
+          <t>4420; 13743</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1544; 8338</t>
+          <t>1382; 8674</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>669; 6367</t>
+          <t>648; 6190</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1600; 9990</t>
+          <t>1498; 9646</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8617; 21266</t>
+          <t>9062; 21189</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4391; 14219</t>
+          <t>4590; 14431</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2940; 10840</t>
+          <t>2681; 11387</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2479; 11482</t>
+          <t>2705; 11857</t>
         </is>
       </c>
     </row>
@@ -2061,17 +2061,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1862; 8476</t>
+          <t>1971; 8907</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3978</t>
+          <t>0; 3507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1295; 7310</t>
+          <t>1284; 8272</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2081,42 +2081,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4021</t>
+          <t>0; 3922</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3246</t>
+          <t>0; 3224</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4422</t>
+          <t>0; 4261</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4667</t>
+          <t>0; 4745</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2702; 10791</t>
+          <t>3013; 10274</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4813</t>
+          <t>0; 4718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1951; 9159</t>
+          <t>1947; 9299</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>0; 4539</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3377; 11876</t>
+          <t>3591; 12778</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1414; 7471</t>
+          <t>1413; 7969</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2671</t>
+          <t>0; 4011</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 99551</t>
+          <t>0; 99907</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1919; 9270</t>
+          <t>1928; 9150</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>601; 5374</t>
+          <t>607; 5196</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4741</t>
+          <t>0; 5283</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1125; 7820</t>
+          <t>1152; 7898</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7090; 17813</t>
+          <t>6852; 17790</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2623; 9886</t>
+          <t>2603; 10896</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>614; 6194</t>
+          <t>603; 6124</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3314; 127422</t>
+          <t>2841; 120811</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12821; 26356</t>
+          <t>13613; 28203</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5359; 15093</t>
+          <t>5181; 16126</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5589; 15446</t>
+          <t>5434; 15144</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3343; 110326</t>
+          <t>3260; 121356</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10112; 22704</t>
+          <t>10573; 23863</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4495; 14371</t>
+          <t>4595; 14072</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3294; 11606</t>
+          <t>3152; 11816</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5221; 17062</t>
+          <t>5599; 16017</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27284; 46386</t>
+          <t>26612; 44725</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11532; 26127</t>
+          <t>12034; 26919</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10137; 22690</t>
+          <t>9970; 22026</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12694; 134992</t>
+          <t>12678; 155409</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P5B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,02</t>
+          <t>0,73; 6,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,77</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 9,28</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,0</t>
+          <t>0,88; 7,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,45; 4,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>1,33; 10,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,98</t>
+          <t>0,83; 5,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,16</t>
+          <t>0,31; 3,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,82</t>
+          <t>0,4; 3,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,03</t>
+          <t>1,16; 6,63</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,92%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,73</t>
+          <t>2,35; 7,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,05</t>
+          <t>0,82; 4,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,74</t>
+          <t>0,32; 3,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,94; 6,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,28</t>
+          <t>1,29; 5,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,49</t>
+          <t>1,15; 5,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,95</t>
+          <t>0,81; 4,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,3</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,64</t>
+          <t>2,27; 5,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,09</t>
+          <t>1,2; 3,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,12</t>
+          <t>0,83; 3,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,48</t>
+          <t>0,83; 3,65</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,36%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,41%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>3,06%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 10,3</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,76</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,38</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,31; 10,82</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,55</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0,86; 5,8</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,8</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,19</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,22</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,24</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,41</t>
+          <t>1,58; 5,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,37</t>
+          <t>0,69; 3,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,68%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,14%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,46</t>
+          <t>1,33; 5,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,93</t>
+          <t>0,46; 4,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,0; 4,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,37</t>
+          <t>0,34; 2,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,18</t>
+          <t>2,34; 8,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,95</t>
+          <t>1,18; 7,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,59</t>
+          <t>0,0; 7,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,95</t>
+          <t>2,27; 5,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,42</t>
+          <t>1,09; 4,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,43</t>
+          <t>0,24; 2,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 20,82</t>
+          <t>0,45; 3,47</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,6</t>
+          <t>1,86; 4,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,39</t>
+          <t>0,88; 2,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,9</t>
+          <t>0,55; 2,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 18,24</t>
+          <t>0,71; 2,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,51</t>
+          <t>2,59; 5,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,62</t>
+          <t>1,18; 3,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,07</t>
+          <t>1,02; 2,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,11</t>
+          <t>0,5; 2,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,33</t>
+          <t>2,53; 4,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,66</t>
+          <t>1,21; 2,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,01</t>
+          <t>0,91; 2,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,9</t>
+          <t>0,75; 2,07</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1519,32 +1519,32 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2110</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1108</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1610</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2207</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3139</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>688; 6299</t>
+          <t>650; 5926</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3958</t>
+          <t>0; 5839</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>467; 4873</t>
+          <t>0; 4742</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>662; 5338</t>
+          <t>0; 3003</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>653; 5307</t>
+          <t>688; 5659</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5372</t>
+          <t>0; 3993</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3946</t>
+          <t>460; 4452</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3799</t>
+          <t>692; 5611</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1372; 8311</t>
+          <t>1384; 8379</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674; 6779</t>
+          <t>668; 6933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>576; 5660</t>
+          <t>792; 6729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1283; 7169</t>
+          <t>1189; 6804</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8141</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4223</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4344</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5465</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4218</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3625</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1441</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8141</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4223</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5833</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2654; 10720</t>
+          <t>4434; 13742</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1721; 8047</t>
+          <t>1594; 8918</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1549; 7352</t>
+          <t>665; 6796</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5479</t>
+          <t>1473; 10259</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4420; 13743</t>
+          <t>2411; 10787</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1382; 8674</t>
+          <t>1827; 9186</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>648; 6190</t>
+          <t>1262; 7490</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1498; 9646</t>
+          <t>0; 4768</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9062; 21189</t>
+          <t>8525; 20540</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4590; 14431</t>
+          <t>4245; 13779</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2681; 11387</t>
+          <t>3013; 11293</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2705; 11857</t>
+          <t>2506; 11043</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,44 +1993,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4636</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3464</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1172</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1348</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>5809</t>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>953</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1971; 8907</t>
+          <t>0; 4389</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3507</t>
+          <t>0; 3233</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1284; 8272</t>
+          <t>0; 4326</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0; 4741</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1995; 9356</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3475</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1237; 8336</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3922</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3224</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4261</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4745</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3013; 10274</t>
+          <t>3005; 10298</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4718</t>
+          <t>0; 4683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1947; 9299</t>
+          <t>1913; 9523</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4539</t>
+          <t>0; 4822</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4578</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7064</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3616</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>657</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27634</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4578</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1922</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1502</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>6580</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3591; 12778</t>
+          <t>1967; 8681</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1413; 7969</t>
+          <t>606; 5263</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4011</t>
+          <t>0; 5744</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 99907</t>
+          <t>998; 7949</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1928; 9150</t>
+          <t>3529; 12505</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>607; 5196</t>
+          <t>1355; 8133</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5283</t>
+          <t>0; 3286</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1152; 7898</t>
+          <t>0; 18969</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6852; 17790</t>
+          <t>6784; 17538</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2603; 10896</t>
+          <t>2700; 10488</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>603; 6124</t>
+          <t>610; 6315</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2841; 120811</t>
+          <t>2487; 19036</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>19275</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>9636</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>9356</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>31282</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>15919</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8349</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41023</t>
+          <t>16506</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13613; 28203</t>
+          <t>9852; 23333</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5181; 16126</t>
+          <t>4738; 14816</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5434; 15144</t>
+          <t>3160; 12253</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3260; 121356</t>
+          <t>4997; 15865</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10573; 23863</t>
+          <t>13041; 27491</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4595; 14072</t>
+          <t>5602; 15733</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3152; 11816</t>
+          <t>5349; 14758</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5599; 16017</t>
+          <t>3141; 17899</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26612; 44725</t>
+          <t>26158; 44427</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12034; 26919</t>
+          <t>12306; 25324</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9970; 22026</t>
+          <t>9986; 22931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12678; 155409</t>
+          <t>9948; 27531</t>
         </is>
       </c>
     </row>
